--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Confounding factor is Issues or factors that may impact on the measurement, not captured in other fields</t>
+    <t>Confounding factor is Issues or factors that may impact on &lt;the measurement&gt;, not captured in other fields</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Confounding factor is Issues or factors that may impact on &lt;the measurement&gt;, not captured in other fields</t>
+    <t>Confounding factor is Issues or factors that may impact on the measurement, not captured in other fields</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>0.9.5</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.5</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.61</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.61</t>
+    <t>0.9.71</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.71</t>
+    <t>0.9.72</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.72</t>
+    <t>0.9.73</t>
   </si>
   <si>
     <t>Name</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Confounding factor is Issues or factors that may impact on the measurement, not captured in other fields</t>
+    <t>Confounding factor is for comments on and records of other incidental factors that may be affect interpretation of the observation, not captured in other fields</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.73</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.74</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Confounding factor is for comments on and records of other incidental factors that may be affect interpretation of the observation, not captured in other fields</t>
+    <t>Confounding factor is Issues or factors that may impact on &lt;the measurement&gt;, not captured in other fields</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsConfoundingFactorExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Confounding factor is Issues or factors that may impact on &lt;the measurement&gt;, not captured in other fields</t>
+    <t>Confounding factor is for comments on and records of other incidental factors that may be affect interpretation of the observation, not captured in other fields</t>
   </si>
   <si>
     <t>Purpose</t>
